--- a/outputs/problem1/problem1_submission.xlsx
+++ b/outputs/problem1/problem1_submission.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1_单点组批" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_运输架次" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_逐箱交付" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_中继架次" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_通信保障" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_分区配置" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1631,13 +1631,13 @@
         <v>0.129</v>
       </c>
       <c r="G11" t="n">
-        <v>1079.225241134656</v>
+        <v>1097.482101486218</v>
       </c>
       <c r="H11" t="n">
-        <v>3.403284441394841</v>
+        <v>3.410375992447635</v>
       </c>
       <c r="I11" t="n">
-        <v>57.45894448256449</v>
+        <v>57.37030009440456</v>
       </c>
     </row>
     <row r="12">
@@ -1779,13 +1779,13 @@
         <v>0.067</v>
       </c>
       <c r="G15" t="n">
-        <v>556.6788066803711</v>
+        <v>559.6308045644856</v>
       </c>
       <c r="H15" t="n">
-        <v>1.075965812127848</v>
+        <v>1.077146138189977</v>
       </c>
       <c r="I15" t="n">
-        <v>73.10085469680378</v>
+        <v>73.07134654525056</v>
       </c>
     </row>
     <row r="16">
